--- a/OUTPUT/direct_Q8UFK2_Agrobacterium_fabrum_str__C58.xlsx
+++ b/OUTPUT/direct_Q8UFK2_Agrobacterium_fabrum_str__C58.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6272</v>
+        <v>0.6271491403438625</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6272</v>
+        <v>0.6271491403438625</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9692</v>
+        <v>0.9690123950419832</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="9">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="10">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="11">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="12">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="13">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="14">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="15">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="16">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="17">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
   </sheetData>
